--- a/jsons/espece_20260905-123950.xlsx
+++ b/jsons/espece_20260905-123950.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\telluris\jsons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC1B254-449F-4236-87AE-06275A4DD8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AFBCED-AC18-40EF-AB72-36AAB2E77D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -3404,6 +3404,9 @@
       <c r="A2" t="s">
         <v>9</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
@@ -3437,6 +3440,9 @@
       <c r="A3" t="s">
         <v>18</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="C3" t="s">
         <v>19</v>
       </c>
@@ -3470,6 +3476,9 @@
       <c r="A4" t="s">
         <v>26</v>
       </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
@@ -3503,6 +3512,9 @@
       <c r="A5" t="s">
         <v>33</v>
       </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
       <c r="C5" t="s">
         <v>34</v>
       </c>
@@ -3536,6 +3548,9 @@
       <c r="A6" t="s">
         <v>40</v>
       </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
       <c r="C6" t="s">
         <v>41</v>
       </c>
@@ -3569,6 +3584,9 @@
       <c r="A7" t="s">
         <v>47</v>
       </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
       <c r="C7" t="s">
         <v>48</v>
       </c>
@@ -3602,6 +3620,9 @@
       <c r="A8" t="s">
         <v>54</v>
       </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
       <c r="C8" t="s">
         <v>55</v>
       </c>
@@ -3635,6 +3656,9 @@
       <c r="A9" t="s">
         <v>61</v>
       </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
       <c r="C9" t="s">
         <v>62</v>
       </c>
@@ -3668,6 +3692,9 @@
       <c r="A10" t="s">
         <v>68</v>
       </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
       <c r="C10" t="s">
         <v>69</v>
       </c>
@@ -3701,6 +3728,9 @@
       <c r="A11" t="s">
         <v>75</v>
       </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
       <c r="C11" t="s">
         <v>76</v>
       </c>
@@ -3734,6 +3764,9 @@
       <c r="A12" t="s">
         <v>82</v>
       </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
       <c r="C12" t="s">
         <v>83</v>
       </c>
@@ -3767,6 +3800,9 @@
       <c r="A13" t="s">
         <v>89</v>
       </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
       <c r="C13" t="s">
         <v>90</v>
       </c>
@@ -3800,6 +3836,9 @@
       <c r="A14" t="s">
         <v>96</v>
       </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
       <c r="C14" t="s">
         <v>97</v>
       </c>
@@ -3833,6 +3872,9 @@
       <c r="A15" t="s">
         <v>103</v>
       </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
       <c r="C15" t="s">
         <v>104</v>
       </c>
@@ -3866,6 +3908,9 @@
       <c r="A16" t="s">
         <v>110</v>
       </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
       <c r="C16" t="s">
         <v>111</v>
       </c>
@@ -3899,6 +3944,9 @@
       <c r="A17" t="s">
         <v>117</v>
       </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
       <c r="C17" t="s">
         <v>118</v>
       </c>
@@ -3932,6 +3980,9 @@
       <c r="A18" t="s">
         <v>124</v>
       </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
       <c r="C18" t="s">
         <v>125</v>
       </c>
@@ -3965,6 +4016,9 @@
       <c r="A19" t="s">
         <v>131</v>
       </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
       <c r="C19" t="s">
         <v>132</v>
       </c>
@@ -3998,6 +4052,9 @@
       <c r="A20" t="s">
         <v>138</v>
       </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
       <c r="C20" t="s">
         <v>139</v>
       </c>
@@ -4031,6 +4088,9 @@
       <c r="A21" t="s">
         <v>145</v>
       </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
       <c r="C21" t="s">
         <v>146</v>
       </c>
@@ -4064,6 +4124,9 @@
       <c r="A22" t="s">
         <v>153</v>
       </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
       <c r="C22" t="s">
         <v>154</v>
       </c>
@@ -4097,6 +4160,9 @@
       <c r="A23" t="s">
         <v>160</v>
       </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
       <c r="C23" t="s">
         <v>161</v>
       </c>
@@ -4130,6 +4196,9 @@
       <c r="A24" t="s">
         <v>168</v>
       </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
       <c r="C24" t="s">
         <v>169</v>
       </c>
@@ -4163,6 +4232,9 @@
       <c r="A25" t="s">
         <v>175</v>
       </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
       <c r="C25" t="s">
         <v>176</v>
       </c>
@@ -4196,6 +4268,9 @@
       <c r="A26" t="s">
         <v>182</v>
       </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
       <c r="C26" t="s">
         <v>183</v>
       </c>
@@ -4229,6 +4304,9 @@
       <c r="A27" t="s">
         <v>189</v>
       </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
       <c r="C27" t="s">
         <v>190</v>
       </c>
@@ -4262,6 +4340,9 @@
       <c r="A28" t="s">
         <v>196</v>
       </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
       <c r="C28" t="s">
         <v>197</v>
       </c>
@@ -4295,6 +4376,9 @@
       <c r="A29" t="s">
         <v>203</v>
       </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
       <c r="C29" t="s">
         <v>204</v>
       </c>
@@ -4328,6 +4412,9 @@
       <c r="A30" t="s">
         <v>211</v>
       </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
       <c r="C30" t="s">
         <v>212</v>
       </c>
@@ -4361,6 +4448,9 @@
       <c r="A31" t="s">
         <v>219</v>
       </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
       <c r="C31" t="s">
         <v>220</v>
       </c>
@@ -4394,6 +4484,9 @@
       <c r="A32" t="s">
         <v>226</v>
       </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
       <c r="C32" t="s">
         <v>227</v>
       </c>
@@ -4427,6 +4520,9 @@
       <c r="A33" t="s">
         <v>233</v>
       </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
       <c r="C33" t="s">
         <v>234</v>
       </c>
@@ -4460,6 +4556,9 @@
       <c r="A34" t="s">
         <v>240</v>
       </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
       <c r="C34" t="s">
         <v>241</v>
       </c>
@@ -4493,6 +4592,9 @@
       <c r="A35" t="s">
         <v>247</v>
       </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
       <c r="C35" t="s">
         <v>248</v>
       </c>
@@ -4526,6 +4628,9 @@
       <c r="A36" t="s">
         <v>254</v>
       </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
       <c r="C36" t="s">
         <v>255</v>
       </c>
@@ -4559,6 +4664,9 @@
       <c r="A37" t="s">
         <v>261</v>
       </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
       <c r="C37" t="s">
         <v>262</v>
       </c>
@@ -4592,6 +4700,9 @@
       <c r="A38" t="s">
         <v>268</v>
       </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
       <c r="C38" t="s">
         <v>269</v>
       </c>
@@ -4625,6 +4736,9 @@
       <c r="A39" t="s">
         <v>275</v>
       </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
       <c r="C39" t="s">
         <v>276</v>
       </c>
@@ -4658,6 +4772,9 @@
       <c r="A40" t="s">
         <v>282</v>
       </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
       <c r="C40" t="s">
         <v>283</v>
       </c>
@@ -4724,6 +4841,9 @@
       <c r="A42" t="s">
         <v>297</v>
       </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
       <c r="C42" t="s">
         <v>298</v>
       </c>
@@ -4790,6 +4910,9 @@
       <c r="A44" t="s">
         <v>311</v>
       </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
       <c r="C44" t="s">
         <v>312</v>
       </c>
@@ -4823,6 +4946,9 @@
       <c r="A45" t="s">
         <v>318</v>
       </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
       <c r="C45" t="s">
         <v>319</v>
       </c>
@@ -4855,6 +4981,9 @@
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>325</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
       </c>
       <c r="C46" t="s">
         <v>326</v>
